--- a/Result/profitability/5536.xlsx
+++ b/Result/profitability/5536.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM72"/>
+  <dimension ref="A1:AM73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>5.02</v>
       </c>
       <c r="M2" t="n">
-        <v>7.1575</v>
+        <v>7.89625</v>
       </c>
       <c r="N2" t="n">
-        <v>19.87</v>
+        <v>19.60625</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>0.75</v>
       </c>
       <c r="M3" t="n">
-        <v>6.61875</v>
+        <v>7.24</v>
       </c>
       <c r="N3" t="n">
-        <v>17.88625</v>
+        <v>17.9425</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="M4" t="n">
-        <v>5.98625</v>
+        <v>6.71</v>
       </c>
       <c r="N4" t="n">
-        <v>16.92</v>
+        <v>17.255</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>2.72</v>
       </c>
       <c r="M5" t="n">
-        <v>5.67875</v>
+        <v>6.18125</v>
       </c>
       <c r="N5" t="n">
-        <v>16.1375</v>
+        <v>16.31</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1131,7 +1131,7 @@
         <v>2.28</v>
       </c>
       <c r="M6" t="n">
-        <v>5.095</v>
+        <v>5.43875</v>
       </c>
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="n">
@@ -1252,7 +1252,7 @@
         <v>1.9</v>
       </c>
       <c r="M7" t="n">
-        <v>4.305</v>
+        <v>4.6675</v>
       </c>
       <c r="N7" t="inlineStr"/>
       <c r="O7" t="n">
@@ -1375,7 +1375,7 @@
         <v>5.86</v>
       </c>
       <c r="M8" t="n">
-        <v>4.02875</v>
+        <v>3.805</v>
       </c>
       <c r="N8" t="inlineStr"/>
       <c r="O8" t="n">
@@ -9546,6 +9546,133 @@
       </c>
       <c r="AM72" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>5536</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C73" t="n">
+        <v>13381</v>
+      </c>
+      <c r="D73" t="n">
+        <v>10620</v>
+      </c>
+      <c r="E73" t="n">
+        <v>2762</v>
+      </c>
+      <c r="F73" t="n">
+        <v>20.64</v>
+      </c>
+      <c r="G73" t="n">
+        <v>2126</v>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>15.89%</t>
+        </is>
+      </c>
+      <c r="I73" t="n">
+        <v>106</v>
+      </c>
+      <c r="J73" t="n">
+        <v>2232</v>
+      </c>
+      <c r="K73" t="n">
+        <v>1361</v>
+      </c>
+      <c r="L73" t="n">
+        <v>10.97</v>
+      </c>
+      <c r="M73" t="n">
+        <v>7.901249999999999</v>
+      </c>
+      <c r="N73" t="n">
+        <v>20.555</v>
+      </c>
+      <c r="O73" t="n">
+        <v>1</v>
+      </c>
+      <c r="P73" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q73" t="n">
+        <v>0</v>
+      </c>
+      <c r="R73" t="n">
+        <v>0</v>
+      </c>
+      <c r="S73" t="n">
+        <v>1</v>
+      </c>
+      <c r="T73" t="n">
+        <v>0</v>
+      </c>
+      <c r="U73" t="n">
+        <v>1</v>
+      </c>
+      <c r="V73" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W73" t="n">
+        <v>-1.789999999999999</v>
+      </c>
+      <c r="X73" t="n">
+        <v>-0.140282131661442</v>
+      </c>
+      <c r="Y73" t="n">
+        <v>-4.739999999999998</v>
+      </c>
+      <c r="Z73" t="n">
+        <v>-0.1867612293144207</v>
+      </c>
+      <c r="AA73" t="n">
+        <v>4.02</v>
+      </c>
+      <c r="AB73" t="n">
+        <v>0.5784172661870504</v>
+      </c>
+      <c r="AC73" t="n">
+        <v>1.379999999999999</v>
+      </c>
+      <c r="AD73" t="n">
+        <v>0.07165109034267902</v>
+      </c>
+      <c r="AE73" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF73" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG73" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH73" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI73" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ73" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK73" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL73" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM73" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
